--- a/Annual_Waterfall_Output.xlsx
+++ b/Annual_Waterfall_Output.xlsx
@@ -557,15 +557,15 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>B8</f>
+        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
         <v/>
       </c>
       <c r="D3" s="6">
-        <f>C8</f>
+        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
         <v/>
       </c>
       <c r="E3" s="6">
-        <f>D8</f>
+        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
         <v/>
       </c>
     </row>
@@ -577,15 +577,15 @@
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>SUMPRODUCT(('Original Data'!C$4:C$103=0)*('Original Data'!O$4:O$103&lt;&gt;0)*'Original Data'!O$4:O$103)*12</f>
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*'Original Data'!$O$4:$O$103)*12</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>SUMPRODUCT(('Original Data'!O$4:O$103=0)*('Original Data'!AA$4:AA$103&lt;&gt;0)*'Original Data'!AA$4:AA$103)*12</f>
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*'Original Data'!$AA$4:$AA$103)*12</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>SUMPRODUCT(('Original Data'!AA$4:AA$103=0)*('Original Data'!AM$4:AM$103&lt;&gt;0)*'Original Data'!AM$4:AM$103)*12</f>
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*'Original Data'!$AM$4:$AM$103)*12</f>
         <v/>
       </c>
     </row>
@@ -597,15 +597,15 @@
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>SUMPRODUCT(('Original Data'!C$4:C$103&gt;0)*('Original Data'!O$4:O$103&gt;0)*('Original Data'!O$4:O$103&gt;'Original Data'!C$4:C$103)*('Original Data'!O$4:O$103-'Original Data'!C$4:C$103))*12</f>
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&gt;'Original Data'!$C$4:$C$103)*('Original Data'!$O$4:$O$103-'Original Data'!$C$4:$C$103))*12</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>SUMPRODUCT(('Original Data'!O$4:O$103&gt;0)*('Original Data'!AA$4:AA$103&gt;0)*('Original Data'!AA$4:AA$103&gt;'Original Data'!O$4:O$103)*('Original Data'!AA$4:AA$103-'Original Data'!O$4:O$103))*12</f>
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;'Original Data'!$O$4:$O$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$O$4:$O$103))*12</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMPRODUCT(('Original Data'!AA$4:AA$103&gt;0)*('Original Data'!AM$4:AM$103&gt;0)*('Original Data'!AM$4:AM$103&gt;'Original Data'!AA$4:AA$103)*('Original Data'!AM$4:AM$103-'Original Data'!AA$4:AA$103))*12</f>
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AA$4:$AA$103))*12</f>
         <v/>
       </c>
     </row>
@@ -617,15 +617,15 @@
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>SUMPRODUCT(('Original Data'!C$4:C$103&gt;0)*('Original Data'!O$4:O$103&gt;0)*('Original Data'!O$4:O$103&lt;'Original Data'!C$4:C$103)*('Original Data'!O$4:O$103-'Original Data'!C$4:C$103))*12</f>
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&lt;'Original Data'!$C$4:$C$103)*('Original Data'!$O$4:$O$103-'Original Data'!$C$4:$C$103))*12</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUMPRODUCT(('Original Data'!O$4:O$103&gt;0)*('Original Data'!AA$4:AA$103&gt;0)*('Original Data'!AA$4:AA$103&lt;'Original Data'!O$4:O$103)*('Original Data'!AA$4:AA$103-'Original Data'!O$4:O$103))*12</f>
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;'Original Data'!$O$4:$O$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$O$4:$O$103))*12</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMPRODUCT(('Original Data'!AA$4:AA$103&gt;0)*('Original Data'!AM$4:AM$103&gt;0)*('Original Data'!AM$4:AM$103&lt;'Original Data'!AA$4:AA$103)*('Original Data'!AM$4:AM$103-'Original Data'!AA$4:AA$103))*12</f>
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AA$4:$AA$103))*12</f>
         <v/>
       </c>
     </row>
@@ -637,15 +637,15 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!C$4:C$103&gt;0)*('Original Data'!O$4:O$103=0)*'Original Data'!C$4:C$103)*12</f>
+        <f>-SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*'Original Data'!$C$4:$C$103)*12</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!O$4:O$103&gt;0)*('Original Data'!AA$4:AA$103=0)*'Original Data'!O$4:O$103)*12</f>
+        <f>-SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*'Original Data'!$O$4:$O$103)*12</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!AA$4:AA$103&gt;0)*('Original Data'!AM$4:AM$103=0)*'Original Data'!AA$4:AA$103)*12</f>
+        <f>-SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*'Original Data'!$AA$4:$AA$103)*12</f>
         <v/>
       </c>
     </row>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>SUMIF('Original Data'!C$4:C$103,"&lt;&gt;"&amp;0)*12</f>
+        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>SUMIF('Original Data'!O$4:O$103,"&lt;&gt;"&amp;0)*12</f>
+        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>SUMIF('Original Data'!AA$4:AA$103,"&lt;&gt;"&amp;0)*12</f>
+        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>SUMIF('Original Data'!AM$4:AM$103,"&lt;&gt;"&amp;0)*12</f>
+        <f>SUM('Original Data'!$AM$4:$AM$103)*12</f>
         <v/>
       </c>
     </row>
@@ -680,15 +680,15 @@
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="10">
-        <f>C8/C3-1</f>
+        <f>IF(C3=0,"",C8/C3-1)</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>D8/D3-1</f>
+        <f>IF(D3=0,"",D8/D3-1)</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>E8/E3-1</f>
+        <f>IF(E3=0,"",E8/E3-1)</f>
         <v/>
       </c>
     </row>
@@ -760,15 +760,15 @@
       </c>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="14">
-        <f>(C3+C6+C7)/C3</f>
+        <f>IF(C3=0,"",(C3+C6+C7)/C3)</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>(D3+D6+D7)/D3</f>
+        <f>IF(D3=0,"",(D3+D6+D7)/D3)</f>
         <v/>
       </c>
       <c r="E13" s="14">
-        <f>(E3+E6+E7)/E3</f>
+        <f>IF(E3=0,"",(E3+E6+E7)/E3)</f>
         <v/>
       </c>
     </row>
@@ -780,15 +780,15 @@
       </c>
       <c r="B14" s="13" t="n"/>
       <c r="C14" s="14">
-        <f>(C3+C7)/C3</f>
+        <f>IF(C3=0,"",(C3+C7)/C3)</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>(D3+D7)/D3</f>
+        <f>IF(D3=0,"",(D3+D7)/D3)</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>(E3+E7)/E3</f>
+        <f>IF(E3=0,"",(E3+E7)/E3)</f>
         <v/>
       </c>
     </row>
@@ -800,15 +800,15 @@
       </c>
       <c r="B15" s="13" t="n"/>
       <c r="C15" s="14">
-        <f>(C3+C5+C6+C7)/C3</f>
+        <f>IF(C3=0,"",(C3+C5+C6+C7)/C3)</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>(D3+D5+D6+D7)/D3</f>
+        <f>IF(D3=0,"",(D3+D5+D6+D7)/D3)</f>
         <v/>
       </c>
       <c r="E15" s="14">
-        <f>(E3+E5+E6+E7)/E3</f>
+        <f>IF(E3=0,"",(E3+E5+E6+E7)/E3)</f>
         <v/>
       </c>
     </row>
@@ -831,15 +831,15 @@
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="16">
-        <f>COUNTIF('Original Data'!C$4:C$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIF('Original Data'!O$4:O$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIF('Original Data'!AA$4:AA$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -851,15 +851,15 @@
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="16">
-        <f>SUMPRODUCT(('Original Data'!C$4:C$103=0)*('Original Data'!O$4:O$103&lt;&gt;0)*1)</f>
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*1)</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>SUMPRODUCT(('Original Data'!O$4:O$103=0)*('Original Data'!AA$4:AA$103&lt;&gt;0)*1)</f>
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*1)</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>SUMPRODUCT(('Original Data'!AA$4:AA$103=0)*('Original Data'!AM$4:AM$103&lt;&gt;0)*1)</f>
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*1)</f>
         <v/>
       </c>
     </row>
@@ -871,15 +871,15 @@
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="17">
-        <f>SUMPRODUCT(('Original Data'!C$4:C$103&gt;0)*('Original Data'!O$4:O$103=0)*1)</f>
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*1)</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>SUMPRODUCT(('Original Data'!O$4:O$103&gt;0)*('Original Data'!AA$4:AA$103=0)*1)</f>
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*1)</f>
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>SUMPRODUCT(('Original Data'!AA$4:AA$103&gt;0)*('Original Data'!AM$4:AM$103=0)*1)</f>
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*1)</f>
         <v/>
       </c>
     </row>
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="B20" s="18">
-        <f>COUNTIF('Original Data'!C$4:C$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
         <v/>
       </c>
       <c r="C20" s="18">
-        <f>COUNTIF('Original Data'!O$4:O$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
         <v/>
       </c>
       <c r="D20" s="18">
-        <f>COUNTIF('Original Data'!AA$4:AA$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
         <v/>
       </c>
       <c r="E20" s="18">
-        <f>COUNTIF('Original Data'!AM$4:AM$103,"&gt;"&amp;0)</f>
+        <f>COUNTIF('Original Data'!$AM$4:$AM$103,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -938,15 +938,15 @@
         </is>
       </c>
       <c r="C22" s="10">
-        <f>IFERROR(C20/C17-1,0)</f>
+        <f>IF(C17=0,"–",C20/C17-1)</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>IFERROR(D20/D17-1,0)</f>
+        <f>IF(D17=0,"–",D20/D17-1)</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>IFERROR(E20/E17-1,0)</f>
+        <f>IF(E17=0,"–",E20/E17-1)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="B23" s="13" t="n"/>
       <c r="C23" s="14">
-        <f>(C17-C19)/C17</f>
+        <f>IF(C17=0,"",(C17-C19)/C17)</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>(D17-D19)/D17</f>
+        <f>IF(D17=0,"",(D17-D19)/D17)</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>(E17-E19)/E17</f>
+        <f>IF(E17=0,"",(E17-E19)/E17)</f>
         <v/>
       </c>
     </row>
@@ -978,15 +978,15 @@
       </c>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(C8/C20,"")</f>
+        <f>IF(C20=0,"",C8/C20)</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IFERROR(D8/D20,"")</f>
+        <f>IF(D20=0,"",D8/D20)</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IFERROR(E8/E20,"")</f>
+        <f>IF(E20=0,"",E8/E20)</f>
         <v/>
       </c>
     </row>
@@ -997,11 +997,11 @@
         </is>
       </c>
       <c r="D25" s="10">
-        <f>IFERROR(D24/C24-1,"")</f>
+        <f>IF(OR(C24=0,C24=""),"",D24/C24-1)</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>IFERROR(E24/D24-1,"")</f>
+        <f>IF(OR(D24=0,D24=""),"",E24/D24-1)</f>
         <v/>
       </c>
     </row>
@@ -1013,15 +1013,15 @@
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(C4/C18,"")</f>
+        <f>IF(C18=0,"",C4/C18)</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IFERROR(D4/D18,"")</f>
+        <f>IF(D18=0,"",D4/D18)</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IFERROR(E4/E18,"")</f>
+        <f>IF(E18=0,"",E4/E18)</f>
         <v/>
       </c>
     </row>
@@ -1032,11 +1032,11 @@
         </is>
       </c>
       <c r="D27" s="21">
-        <f>IFERROR(D26/C26-1,"")</f>
+        <f>IF(OR(C26=0,C26=""),"",D26/C26-1)</f>
         <v/>
       </c>
       <c r="E27" s="21">
-        <f>IFERROR(E26/D26-1,"")</f>
+        <f>IF(OR(D26=0,D26=""),"",E26/D26-1)</f>
         <v/>
       </c>
     </row>
@@ -1048,15 +1048,15 @@
       </c>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(ABS(C7)/C19,"")</f>
+        <f>IF(C19=0,"",-C7/C19)</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IFERROR(ABS(D7)/D19,"")</f>
+        <f>IF(D19=0,"",-D7/D19)</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IFERROR(ABS(E7)/E19,"")</f>
+        <f>IF(E19=0,"",-E7/E19)</f>
         <v/>
       </c>
     </row>
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="D29" s="21">
-        <f>IFERROR(D28/C28-1,"")</f>
+        <f>IF(OR(C28=0,C28=""),"",D28/C28-1)</f>
         <v/>
       </c>
       <c r="E29" s="21">
-        <f>IFERROR(E28/D28-1,"")</f>
+        <f>IF(OR(D28=0,D28=""),"",E28/D28-1)</f>
         <v/>
       </c>
     </row>
